--- a/TestData/TMTI0056875_56876_56877_VerifyNewJobTypeOnOpportunityEngagementManagerJobTypeObjPage.xlsx
+++ b/TestData/TMTI0056875_56876_56877_VerifyNewJobTypeOnOpportunityEngagementManagerJobTypeObjPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B71708-D1AA-4E9D-93F9-44075BE99398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12E86B6-84F5-4668-9AAC-A02CE29CC770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="1185" yWindow="435" windowWidth="21600" windowHeight="10740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="5532" yWindow="3024" windowWidth="17244" windowHeight="8352" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -860,13 +860,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -874,7 +874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -882,7 +882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -890,7 +890,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -898,7 +898,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -906,7 +906,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -914,7 +914,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -922,7 +922,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -938,13 +938,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9DE9B1-D193-42A1-A5D5-A99A375F2944}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -955,7 +955,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -966,7 +966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -977,7 +977,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -988,7 +988,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -999,7 +999,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>23</v>
       </c>
